--- a/all/full_merged_data_manual_fix.xlsx
+++ b/all/full_merged_data_manual_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trevo\OneDrive\Documents\GitHub\TEdissy_analysis\all\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FDD932-9B6E-4AC5-BD56-99F85BCA9F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8D02CA-9ECE-4C50-8674-1B88ABE2D222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{EBB55AC1-2973-4C7E-8DDF-BB4A445C307E}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10180" xr2:uid="{EBB55AC1-2973-4C7E-8DDF-BB4A445C307E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,9 +62,6 @@
     <t>variety</t>
   </si>
   <si>
-    <t>Life_S</t>
-  </si>
-  <si>
     <t>carb_mg_per_g_mean</t>
   </si>
   <si>
@@ -252,6 +249,9 @@
   </si>
   <si>
     <t>Ilo Mariculture Powder</t>
+  </si>
+  <si>
+    <t>life stage</t>
   </si>
 </sst>
 </file>
@@ -656,7 +656,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
@@ -668,39 +668,39 @@
         <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>34.8410733262455</v>
@@ -732,19 +732,19 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3">
         <v>18.054735905649</v>
@@ -776,19 +776,19 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F4">
         <v>40.088267484506197</v>
@@ -820,19 +820,19 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>23.155422724887298</v>
@@ -844,10 +844,10 @@
         <v>4.4878285888996103E-2</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K5" s="2">
         <v>0.44393398105887</v>
@@ -864,19 +864,19 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>28.846502984407799</v>
@@ -888,13 +888,13 @@
         <v>2.9366270201924002E-2</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L6">
         <v>0.69849041199999995</v>
@@ -908,19 +908,19 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>47.3358519454682</v>
@@ -932,10 +932,10 @@
         <v>4.4104119829941002E-2</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K7" s="2">
         <v>0.248</v>
@@ -952,19 +952,19 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8">
         <v>27.809505333897501</v>
@@ -976,10 +976,10 @@
         <v>0.16576472593195599</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K8" s="2">
         <v>0.27828386717602299</v>
@@ -996,19 +996,19 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9">
         <v>24.745919828432299</v>
@@ -1040,19 +1040,19 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10">
         <v>31.595581110083099</v>
@@ -1084,19 +1084,19 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11">
         <v>30.032073450312001</v>
@@ -1128,19 +1128,19 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12">
         <v>34.0868831449488</v>
@@ -1172,19 +1172,19 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13">
         <v>41.635403747769899</v>
@@ -1216,19 +1216,19 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
         <v>34</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F14">
         <v>40.260847303667902</v>
@@ -1260,19 +1260,19 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15">
         <v>36.982861391564903</v>
@@ -1304,19 +1304,19 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16">
         <v>26.318953770463899</v>
@@ -1348,19 +1348,19 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
         <v>39</v>
       </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17">
         <v>28.233181597066299</v>
@@ -1392,19 +1392,19 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18">
         <v>20.626955080917</v>
@@ -1436,16 +1436,16 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F19">
         <v>30.437683273839301</v>
@@ -1457,10 +1457,10 @@
         <v>1.78176099518297E-2</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K19">
         <v>0.33977983337662099</v>
@@ -1477,19 +1477,19 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20">
         <v>42.125770771172398</v>
@@ -1521,19 +1521,19 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
         <v>44</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>45</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
         <v>46</v>
-      </c>
-      <c r="D21" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" t="s">
-        <v>47</v>
       </c>
       <c r="F21">
         <v>27.113006083778</v>
@@ -1565,19 +1565,19 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
         <v>45</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" t="s">
         <v>46</v>
-      </c>
-      <c r="D22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" t="s">
-        <v>47</v>
       </c>
       <c r="F22">
         <v>30.218044658163102</v>
@@ -1609,19 +1609,19 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
         <v>45</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" t="s">
         <v>46</v>
-      </c>
-      <c r="D23" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" t="s">
-        <v>47</v>
       </c>
       <c r="F23">
         <v>27.673816363442398</v>
@@ -1653,19 +1653,19 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F24">
         <v>45.781799703788799</v>
@@ -1677,39 +1677,39 @@
         <v>7.3593287935716595E-2</v>
       </c>
       <c r="I24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F25">
         <v>36.072782556335603</v>
@@ -1721,39 +1721,39 @@
         <v>5.8791022069805403E-2</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26">
         <v>45.599169238661503</v>
@@ -1765,39 +1765,39 @@
         <v>1.2365068215171899E-2</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F27">
         <v>35.962677219014303</v>
@@ -1809,39 +1809,39 @@
         <v>0.113495633698162</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
         <v>15</v>
       </c>
-      <c r="C28" t="s">
-        <v>16</v>
-      </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F28">
         <v>37.8556956054002</v>
@@ -1853,39 +1853,39 @@
         <v>3.43403749716771E-2</v>
       </c>
       <c r="I28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
         <v>15</v>
       </c>
-      <c r="C29" t="s">
-        <v>16</v>
-      </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29">
         <v>34.416291308360002</v>
@@ -1897,39 +1897,39 @@
         <v>2.77910003843309E-2</v>
       </c>
       <c r="I29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
         <v>15</v>
       </c>
-      <c r="C30" t="s">
-        <v>16</v>
-      </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F30">
         <v>43.021422386355098</v>
@@ -1941,39 +1941,39 @@
         <v>0.22020640218927201</v>
       </c>
       <c r="I30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
         <v>15</v>
       </c>
-      <c r="C31" t="s">
-        <v>16</v>
-      </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F31">
         <v>28.558572121771199</v>
@@ -1985,39 +1985,39 @@
         <v>1.5305962276120799E-2</v>
       </c>
       <c r="I31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
         <v>15</v>
       </c>
-      <c r="C32" t="s">
-        <v>16</v>
-      </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F32">
         <v>48.724815427428098</v>
@@ -2029,39 +2029,39 @@
         <v>6.9648086165781706E-2</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
         <v>15</v>
       </c>
-      <c r="C33" t="s">
-        <v>16</v>
-      </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F33">
         <v>47.265895113273899</v>
@@ -2073,39 +2073,39 @@
         <v>4.7514081223191798E-2</v>
       </c>
       <c r="I33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
         <v>15</v>
       </c>
-      <c r="C34" t="s">
-        <v>16</v>
-      </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F34">
         <v>44.278597196648803</v>
@@ -2117,39 +2117,39 @@
         <v>0.114522194289329</v>
       </c>
       <c r="I34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
         <v>15</v>
       </c>
-      <c r="C35" t="s">
-        <v>16</v>
-      </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F35">
         <v>32.706872053032399</v>
@@ -2161,39 +2161,39 @@
         <v>7.7156677095588003E-2</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F36">
         <v>32.636204162279697</v>
@@ -2205,39 +2205,39 @@
         <v>0.18530158528308699</v>
       </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F37">
         <v>32.653177896408501</v>
@@ -2249,39 +2249,39 @@
         <v>0.14064824917486801</v>
       </c>
       <c r="I37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" t="s">
         <v>35</v>
       </c>
-      <c r="C38" t="s">
-        <v>36</v>
-      </c>
       <c r="D38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F38">
         <v>30.263094871726999</v>
@@ -2293,39 +2293,39 @@
         <v>8.7978019459641205E-2</v>
       </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" t="s">
         <v>35</v>
       </c>
-      <c r="C39" t="s">
-        <v>36</v>
-      </c>
       <c r="D39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F39">
         <v>43.514667238385996</v>
@@ -2337,39 +2337,39 @@
         <v>4.9263274883099097E-2</v>
       </c>
       <c r="I39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F40">
         <v>41.848235527197097</v>
@@ -2381,39 +2381,39 @@
         <v>9.7126296444934701E-2</v>
       </c>
       <c r="I40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F41">
         <v>48.160128716965801</v>
@@ -2425,39 +2425,39 @@
         <v>7.9365861254275694E-2</v>
       </c>
       <c r="I41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F42">
         <v>31.5339798665972</v>
@@ -2469,42 +2469,42 @@
         <v>2.5122704130106699E-2</v>
       </c>
       <c r="I42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G43">
         <v>2.7819533130953599E-2</v>
@@ -2513,22 +2513,22 @@
         <v>3.7621503889139603E-2</v>
       </c>
       <c r="I43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
